--- a/links/Juegos_XBOX.xlsx
+++ b/links/Juegos_XBOX.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:Q21"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
     <col min="7" max="7" width="35.83203125" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
@@ -416,18 +416,6 @@
     <col min="15" max="15" width="35.83203125" customWidth="1"/>
     <col min="16" max="16" width="35.83203125" customWidth="1"/>
     <col min="17" max="17" width="35.83203125" customWidth="1"/>
-    <col min="18" max="18" width="35.83203125" customWidth="1"/>
-    <col min="19" max="19" width="35.83203125" customWidth="1"/>
-    <col min="20" max="20" width="35.83203125" customWidth="1"/>
-    <col min="21" max="21" width="35.83203125" customWidth="1"/>
-    <col min="22" max="22" width="35.83203125" customWidth="1"/>
-    <col min="23" max="23" width="35.83203125" customWidth="1"/>
-    <col min="24" max="24" width="35.83203125" customWidth="1"/>
-    <col min="25" max="25" width="35.83203125" customWidth="1"/>
-    <col min="26" max="26" width="35.83203125" customWidth="1"/>
-    <col min="27" max="27" width="35.83203125" customWidth="1"/>
-    <col min="28" max="28" width="35.83203125" customWidth="1"/>
-    <col min="29" max="29" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,78 +432,42 @@
         <v>Imagen Local</v>
       </c>
       <c r="E1" t="str">
+        <v>Sinopsis</v>
+      </c>
+      <c r="F1" t="str">
         <v>En Varias Partes</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Mega</v>
       </c>
-      <c r="G1" t="str">
-        <v>Mega Parte 1</v>
-      </c>
       <c r="H1" t="str">
-        <v>Mega Parte 2</v>
+        <v>Mediafire</v>
       </c>
       <c r="I1" t="str">
-        <v>Mega Parte 3</v>
+        <v>1Fichier</v>
       </c>
       <c r="J1" t="str">
-        <v>Mediafire</v>
+        <v>Google Drive</v>
       </c>
       <c r="K1" t="str">
-        <v>1Fichier</v>
+        <v>Qiwi</v>
       </c>
       <c r="L1" t="str">
-        <v>1Fichier Parte 1</v>
+        <v>Pixeldrain</v>
       </c>
       <c r="M1" t="str">
-        <v>1Fichier Parte 2</v>
+        <v>Megaup</v>
       </c>
       <c r="N1" t="str">
-        <v>1Fichier Parte 3</v>
+        <v>Otro Link 1</v>
       </c>
       <c r="O1" t="str">
-        <v>1Fichier Parte 4</v>
+        <v>Otro Link 2</v>
       </c>
       <c r="P1" t="str">
-        <v>1Fichier Parte 5</v>
+        <v>Otro Link 3</v>
       </c>
       <c r="Q1" t="str">
-        <v>1Fichier Parte 6</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Google Drive</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Google Drive Parte 1</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Google Drive Parte 2</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Google Drive Parte 3</v>
-      </c>
-      <c r="V1" t="str">
-        <v>Google Drive Parte 4</v>
-      </c>
-      <c r="W1" t="str">
-        <v>Qiwi</v>
-      </c>
-      <c r="X1" t="str">
-        <v>Pixeldrain</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>Megaup</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>Otro Link 1</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>Otro Link 2</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>Otro Link 3</v>
-      </c>
-      <c r="AC1" t="str">
         <v>Otro Link 4</v>
       </c>
     </row>
@@ -533,24 +485,15 @@
         <v>imagenes/XBOX/FIFA 21 Mod [Jtag-RGH].jpg</v>
       </c>
       <c r="E2" t="str">
-        <v>No</v>
-      </c>
-      <c r="J2" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F2" t="str">
+        <v>No</v>
+      </c>
+      <c r="H2" t="str">
         <v>https://www.mediafire.com/folder/rb1mj8sv83s7g/FIFA+2021+RGH</v>
       </c>
-      <c r="L2" t="str">
-        <v>https://1fichier.com/?0gbgpgem2r8oxahgyzt3</v>
-      </c>
-      <c r="M2" t="str">
-        <v>https://filecrypt.cc/Container/BCC182AAEC.html</v>
-      </c>
-      <c r="S2" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T2" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z2" t="str">
+      <c r="N2" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -568,15 +511,12 @@
         <v>imagenes/XBOX/Geesen Love Plus Pengo [NTSC-J][ISO].jpg</v>
       </c>
       <c r="E3" t="str">
-        <v>No</v>
-      </c>
-      <c r="S3" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T3" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z3" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F3" t="str">
+        <v>No</v>
+      </c>
+      <c r="N3" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -594,15 +534,12 @@
         <v>imagenes/XBOX/Just Dance 2019 [Region Free][ISO].jpg</v>
       </c>
       <c r="E4" t="str">
-        <v>No</v>
-      </c>
-      <c r="S4" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T4" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z4" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F4" t="str">
+        <v>No</v>
+      </c>
+      <c r="N4" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -620,27 +557,24 @@
         <v>imagenes/XBOX/Just Dance 2019 [Jtag-RGH].jpg</v>
       </c>
       <c r="E5" t="str">
-        <v>No</v>
-      </c>
-      <c r="J5" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F5" t="str">
+        <v>No</v>
+      </c>
+      <c r="H5" t="str">
         <v>https://www.mediafire.com/folder/5mmmlp5eijgen/Just+Dance+2019+Rgh</v>
       </c>
-      <c r="K5" t="str">
+      <c r="I5" t="str">
         <v>https://1fichier.com/?j63gur0tkdgyx25u3w06</v>
       </c>
-      <c r="S5" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T5" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z5" t="str">
+      <c r="N5" t="str">
         <v>https://dlxbgame.com/guide-download-game/</v>
       </c>
-      <c r="AA5" t="str">
+      <c r="O5" t="str">
         <v>https://dlxbgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AB5" t="str">
+      <c r="P5" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -658,15 +592,12 @@
         <v>imagenes/XBOX/FIFA 19 [Region Free][PAL][NTSC][ISO].jpg</v>
       </c>
       <c r="E6" t="str">
-        <v>No</v>
-      </c>
-      <c r="S6" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T6" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z6" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F6" t="str">
+        <v>No</v>
+      </c>
+      <c r="N6" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -684,27 +615,18 @@
         <v>imagenes/XBOX/FIFA 19 [Jtag-RGH].jpg</v>
       </c>
       <c r="E7" t="str">
-        <v>No</v>
-      </c>
-      <c r="L7" t="str">
-        <v>https://1fichier.com/?xi2grml8sipqq08p1tve</v>
-      </c>
-      <c r="M7" t="str">
-        <v>https://filecrypt.cc/Container/3108B7D8E9.html</v>
-      </c>
-      <c r="S7" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T7" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z7" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F7" t="str">
+        <v>No</v>
+      </c>
+      <c r="N7" t="str">
         <v>https://dlxbgame.com/guide-download-game/</v>
       </c>
-      <c r="AA7" t="str">
+      <c r="O7" t="str">
         <v>https://dlxbgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AB7" t="str">
+      <c r="P7" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -722,15 +644,12 @@
         <v>imagenes/XBOX/Shiei No Sona nyl Refrain What a Beautiful Memorie.jpg</v>
       </c>
       <c r="E8" t="str">
-        <v>No</v>
-      </c>
-      <c r="S8" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T8" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z8" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F8" t="str">
+        <v>No</v>
+      </c>
+      <c r="N8" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -748,15 +667,12 @@
         <v>imagenes/XBOX/Root Double Before Crime After Days [NTSC-J][ISO].jpg</v>
       </c>
       <c r="E9" t="str">
-        <v>No</v>
-      </c>
-      <c r="S9" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T9" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z9" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F9" t="str">
+        <v>No</v>
+      </c>
+      <c r="N9" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -774,18 +690,15 @@
         <v>imagenes/XBOX/Just Dance 2018 [Jtag-RGH].jpg</v>
       </c>
       <c r="E10" t="str">
-        <v>No</v>
-      </c>
-      <c r="K10" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F10" t="str">
+        <v>No</v>
+      </c>
+      <c r="I10" t="str">
         <v>https://1fichier.com/?xu2cl5i67u6r50lp6ti1</v>
       </c>
-      <c r="S10" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T10" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z10" t="str">
+      <c r="N10" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -803,18 +716,15 @@
         <v>imagenes/XBOX/Just Dance 2018 [PAL][NTSC-J][ISO].jpg</v>
       </c>
       <c r="E11" t="str">
-        <v>No</v>
-      </c>
-      <c r="S11" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T11" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z11" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F11" t="str">
+        <v>No</v>
+      </c>
+      <c r="N11" t="str">
         <v>https://dlxbgame.com/guide-download-game/: https://dlxbgame.com/guide-download-game/</v>
       </c>
-      <c r="AA11" t="str">
+      <c r="O11" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -832,15 +742,12 @@
         <v>imagenes/XBOX/FIFA 18 [Region Free][PAL][NTSC][ISO].jpg</v>
       </c>
       <c r="E12" t="str">
-        <v>No</v>
-      </c>
-      <c r="S12" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T12" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z12" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F12" t="str">
+        <v>No</v>
+      </c>
+      <c r="N12" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -858,39 +765,18 @@
         <v>imagenes/XBOX/FIFA 18 [Jtag-RGH].jpg</v>
       </c>
       <c r="E13" t="str">
-        <v>No</v>
-      </c>
-      <c r="L13" t="str">
-        <v>https://1fichier.com/?yy9zqyh4makzgq7mcopd</v>
-      </c>
-      <c r="M13" t="str">
-        <v>https://1fichier.com/?dk5v0fan3r2jbgdvvqbo</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F13" t="str">
+        <v>No</v>
       </c>
       <c r="N13" t="str">
-        <v>https://1fichier.com/?61iahw43i1l8u5p41au4</v>
+        <v>https://dlxbgame.com/guide-download-game/: https://dlxbgame.com/guide-download-game/</v>
       </c>
       <c r="O13" t="str">
-        <v>https://1fichier.com/?pzfejqkpny4rbjd5nvac</v>
+        <v>https://dlxbgame.com/guide-resolve-error-not-download-file/: https://dlxbgame.com/guide-resolve-error-not-download-file/</v>
       </c>
       <c r="P13" t="str">
-        <v>https://1fichier.com/?y9j7repwa9f1y984f4f5</v>
-      </c>
-      <c r="Q13" t="str">
-        <v>https://1fichier.com/?jb8bv35m4m440tfkhfmz</v>
-      </c>
-      <c r="S13" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T13" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z13" t="str">
-        <v>https://dlxbgame.com/guide-download-game/: https://dlxbgame.com/guide-download-game/</v>
-      </c>
-      <c r="AA13" t="str">
-        <v>https://dlxbgame.com/guide-resolve-error-not-download-file/: https://dlxbgame.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="AB13" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -908,21 +794,18 @@
         <v>imagenes/XBOX/NBA 2K18 [Jtag-RGH].jpg</v>
       </c>
       <c r="E14" t="str">
-        <v>No</v>
-      </c>
-      <c r="J14" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No</v>
+      </c>
+      <c r="H14" t="str">
         <v>https://www.mediafire.com/folder/e2kdsr5lbc6d6/NBA_2K2018_Rgh</v>
       </c>
-      <c r="K14" t="str">
+      <c r="I14" t="str">
         <v>https://1fichier.com/?plcamsva2piuwgso0od1</v>
       </c>
-      <c r="S14" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T14" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z14" t="str">
+      <c r="N14" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -940,15 +823,12 @@
         <v>imagenes/XBOX/NBA 2K18 [Region Free][ISO].jpg</v>
       </c>
       <c r="E15" t="str">
-        <v>No</v>
-      </c>
-      <c r="S15" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T15" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z15" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F15" t="str">
+        <v>No</v>
+      </c>
+      <c r="N15" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -966,36 +846,15 @@
         <v>imagenes/XBOX/Pro Evolution Soccer 2018 [PES 2018][Jtag-RGH].jpg</v>
       </c>
       <c r="E16" t="str">
-        <v>No</v>
-      </c>
-      <c r="G16" t="str">
-        <v>https://goo.gl/GrNqKp</v>
+        <v>No disponible</v>
+      </c>
+      <c r="F16" t="str">
+        <v>No</v>
       </c>
       <c r="H16" t="str">
-        <v>https://goo.gl/N6yseu</v>
-      </c>
-      <c r="I16" t="str">
-        <v>https://goo.gl/96TWuc</v>
-      </c>
-      <c r="J16" t="str">
         <v>https://www.mediafire.com/folder/4q6xgz78oxc7j/Pes_2018_rgh</v>
       </c>
-      <c r="L16" t="str">
-        <v>https://1fichier.com/?ma4mqne246fpu36w6i7i</v>
-      </c>
-      <c r="M16" t="str">
-        <v>https://1fichier.com/?1ugw15b5s8bcgqljrrkr</v>
-      </c>
       <c r="N16" t="str">
-        <v>https://1fichier.com/?lknb82a51ziii94fberz</v>
-      </c>
-      <c r="S16" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T16" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z16" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1013,15 +872,12 @@
         <v>imagenes/XBOX/Pro Evolution Soccer 2018 [PES 2018][NTSC-U][PAL][.jpg</v>
       </c>
       <c r="E17" t="str">
-        <v>No</v>
-      </c>
-      <c r="S17" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T17" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z17" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F17" t="str">
+        <v>No</v>
+      </c>
+      <c r="N17" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1039,15 +895,12 @@
         <v>imagenes/XBOX/Minecraft Story Mode Season Two The Telltale Serie.jpg</v>
       </c>
       <c r="E18" t="str">
-        <v>No</v>
-      </c>
-      <c r="S18" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T18" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z18" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F18" t="str">
+        <v>No</v>
+      </c>
+      <c r="N18" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1065,30 +918,21 @@
         <v>imagenes/XBOX/Disney Pixar Cars 3 Driven To Win [Jtag-RGH].jpg</v>
       </c>
       <c r="E19" t="str">
-        <v>No</v>
-      </c>
-      <c r="J19" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F19" t="str">
+        <v>No</v>
+      </c>
+      <c r="H19" t="str">
         <v>https://www.mediafire.com/file/uk2ocmdl162gk2t/CARS_3_AnDreXplay.rar/file</v>
       </c>
-      <c r="K19" t="str">
+      <c r="I19" t="str">
         <v>https://1fichier.com/?adtlq5jrb7fnc57si43p</v>
       </c>
-      <c r="S19" t="str">
-        <v>https://downloadgameps3.com/guide-fix-error-limit-download-google-drive/: https://downloadgameps3.com/guide-fix-error-limit-download-google-drive/</v>
-      </c>
-      <c r="T19" t="str">
-        <v>https://dlxbgame.com/cars-3-driven-win-iso-complex-region-free/</v>
-      </c>
-      <c r="U19" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="V19" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z19" t="str">
+      <c r="N19" t="str">
         <v>https://downloadgameps3.com/guide-download-game/: https://downloadgameps3.com/guide-download-game/</v>
       </c>
-      <c r="AA19" t="str">
+      <c r="O19" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1106,24 +950,21 @@
         <v>imagenes/XBOX/Disney Pixar Cars 3 Driven To Win [Region Free][IS.jpg</v>
       </c>
       <c r="E20" t="str">
-        <v>No</v>
-      </c>
-      <c r="S20" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T20" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z20" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F20" t="str">
+        <v>No</v>
+      </c>
+      <c r="N20" t="str">
         <v>https://dlxbgame.com/guide-download-game/</v>
       </c>
-      <c r="AA20" t="str">
+      <c r="O20" t="str">
         <v>https://dlxbgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AB20" t="str">
+      <c r="P20" t="str">
         <v>https://dlxbgame.com/guide-resolve-error-not-download-file/: https://dlxbgame.com/guide-resolve-error-not-download-file/</v>
       </c>
-      <c r="AC20" t="str">
+      <c r="Q20" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
@@ -1141,33 +982,30 @@
         <v>imagenes/XBOX/Code 18 [Jtag-RGH].jpg</v>
       </c>
       <c r="E21" t="str">
-        <v>No</v>
-      </c>
-      <c r="J21" t="str">
+        <v>No disponible</v>
+      </c>
+      <c r="F21" t="str">
+        <v>No</v>
+      </c>
+      <c r="H21" t="str">
         <v>https://www.mediafire.com/file/yf8g71nzzdrz77j/Cod18+AnDreX.rar/file</v>
       </c>
-      <c r="K21" t="str">
+      <c r="I21" t="str">
         <v>https://1fichier.com/?d2t9atdgvwvm5iihp5e4</v>
       </c>
-      <c r="S21" t="str">
-        <v>http://downloadgamexbox.com/guide-resolve-error-not-download-file/</v>
-      </c>
-      <c r="T21" t="str">
-        <v>https://downloadgamexbox.com/how-to-download-link-google-drive-by-idm/</v>
-      </c>
-      <c r="Z21" t="str">
+      <c r="N21" t="str">
         <v>https://dlxbgame.com/guide-download-game/</v>
       </c>
-      <c r="AA21" t="str">
+      <c r="O21" t="str">
         <v>https://dlxbgame.com/guide-download-game-use-jdownload/</v>
       </c>
-      <c r="AB21" t="str">
+      <c r="P21" t="str">
         <v>https://downloadgameps3.net/archives/18667</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q21"/>
   </ignoredErrors>
 </worksheet>
 </file>